--- a/data/excel/cammesa_gu_actividad_mensual.xlsx
+++ b/data/excel/cammesa_gu_actividad_mensual.xlsx
@@ -10375,7 +10375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T19:43:33Z</t>
+          <t>2026-10-24T05:02:43Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/cammesa_gu_actividad_mensual.xlsx
+++ b/data/excel/cammesa_gu_actividad_mensual.xlsx
@@ -10375,7 +10375,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24T05:02:43Z</t>
+          <t>2026-10-31T06:18:29Z</t>
         </is>
       </c>
     </row>
